--- a/templates/FDI_Master.xlsx
+++ b/templates/FDI_Master.xlsx
@@ -98,7 +98,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -120,11 +120,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -147,6 +191,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1085,11 +1131,6 @@
           <t>FORMATO DE DOCUMENTOS INICIALES (FDI)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1097,11 +1138,6 @@
           <t>Datos de cotización</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1116,11 +1152,6 @@
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1129,8 +1160,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1139,8 +1170,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1149,8 +1180,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1159,8 +1190,8 @@
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1169,8 +1200,8 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1179,8 +1210,8 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1189,8 +1220,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1198,11 +1229,6 @@
           <t>Envío</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1211,8 +1237,8 @@
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1221,8 +1247,8 @@
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1231,8 +1257,8 @@
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1241,8 +1267,8 @@
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1251,8 +1277,8 @@
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="15" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1260,11 +1286,6 @@
           <t>Comercial</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1273,8 +1294,8 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1283,8 +1304,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1293,8 +1314,8 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1303,8 +1324,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1313,8 +1334,8 @@
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="15" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1322,11 +1343,6 @@
           <t>Fechas</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1335,8 +1351,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1345,8 +1361,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1354,11 +1370,6 @@
           <t>Notas</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1367,8 +1378,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -1377,8 +1388,8 @@
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B19:D19"/>
@@ -1428,11 +1439,6 @@
           <t>SISTEMA — Mezzanine limpio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1447,11 +1453,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1460,8 +1461,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1470,8 +1471,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1480,8 +1481,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1490,8 +1491,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1499,11 +1500,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -1511,11 +1507,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1524,8 +1515,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1534,8 +1525,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1544,8 +1535,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1553,11 +1544,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -1634,11 +1620,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1647,8 +1628,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -1668,11 +1649,6 @@
           <t>D) CAPTURA POR DISEÑO — Mezzanine limpio</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1680,11 +1656,6 @@
           <t>Configuración del mezzanine</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1693,8 +1664,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1703,8 +1674,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1713,8 +1684,8 @@
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -1723,8 +1694,8 @@
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1733,8 +1704,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -1743,8 +1714,8 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1753,8 +1724,8 @@
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1763,8 +1734,8 @@
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="15" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Rejilla Irving / MDF</t>
@@ -1778,8 +1749,8 @@
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -1788,8 +1759,8 @@
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -1798,8 +1769,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -1808,8 +1779,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -1818,8 +1789,8 @@
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1828,8 +1799,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1838,8 +1809,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -1847,11 +1818,6 @@
           <t>Configuración de columnas</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -1860,8 +1826,8 @@
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="15" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Manual / Por cálculo</t>
@@ -1875,8 +1841,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -1884,11 +1850,6 @@
           <t>Producto (zona modulada)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -1896,11 +1857,6 @@
           <t>Productos (un renglón por producto)</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
@@ -1972,11 +1928,6 @@
           <t>Tarima (zona no modulada)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -1984,11 +1935,6 @@
           <t>Tarimas</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="12" t="n"/>
-      <c r="F56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
@@ -2069,11 +2015,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -2082,8 +2023,8 @@
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -2092,8 +2033,8 @@
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="C65" s="14" t="n"/>
+      <c r="D65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -2102,8 +2043,8 @@
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="C66" s="14" t="n"/>
+      <c r="D66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -2111,11 +2052,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="12" t="n"/>
-      <c r="F67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -2124,8 +2060,8 @@
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -2134,8 +2070,8 @@
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
-      <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="C69" s="14" t="n"/>
+      <c r="D69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -2144,8 +2080,8 @@
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="C70" s="14" t="n"/>
+      <c r="D70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -2154,8 +2090,8 @@
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
-      <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="C71" s="14" t="n"/>
+      <c r="D71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -2164,8 +2100,8 @@
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -2174,8 +2110,8 @@
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="C73" s="14" t="n"/>
+      <c r="D73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -2183,11 +2119,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
@@ -2232,11 +2163,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
@@ -2276,11 +2202,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -2288,11 +2209,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -2301,8 +2217,8 @@
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="15" t="n"/>
       <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -2316,8 +2232,8 @@
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -2326,8 +2242,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -2336,8 +2252,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="15" t="n"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -2350,11 +2266,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="12" t="n"/>
-      <c r="F93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
@@ -2390,11 +2301,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B100" s="12" t="n"/>
-      <c r="C100" s="12" t="n"/>
-      <c r="D100" s="12" t="n"/>
-      <c r="E100" s="12" t="n"/>
-      <c r="F100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -2403,8 +2309,8 @@
         </is>
       </c>
       <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
+      <c r="C101" s="14" t="n"/>
+      <c r="D101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -2413,8 +2319,8 @@
         </is>
       </c>
       <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="C102" s="14" t="n"/>
+      <c r="D102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -2423,8 +2329,8 @@
         </is>
       </c>
       <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
+      <c r="C103" s="14" t="n"/>
+      <c r="D103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -2433,8 +2339,8 @@
         </is>
       </c>
       <c r="B104" s="8" t="n"/>
-      <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
+      <c r="C104" s="14" t="n"/>
+      <c r="D104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -2443,8 +2349,8 @@
         </is>
       </c>
       <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
+      <c r="C105" s="14" t="n"/>
+      <c r="D105" s="15" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -2453,8 +2359,8 @@
         </is>
       </c>
       <c r="B106" s="8" t="n"/>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
+      <c r="C106" s="14" t="n"/>
+      <c r="D106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -2463,8 +2369,8 @@
         </is>
       </c>
       <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
+      <c r="C107" s="14" t="n"/>
+      <c r="D107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
@@ -2473,8 +2379,8 @@
         </is>
       </c>
       <c r="B108" s="8" t="n"/>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
+      <c r="C108" s="14" t="n"/>
+      <c r="D108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
@@ -2482,11 +2388,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B109" s="12" t="n"/>
-      <c r="C109" s="12" t="n"/>
-      <c r="D109" s="12" t="n"/>
-      <c r="E109" s="12" t="n"/>
-      <c r="F109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
@@ -2519,8 +2420,8 @@
         </is>
       </c>
       <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
+      <c r="C115" s="14" t="n"/>
+      <c r="D115" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="76">
@@ -2536,12 +2437,12 @@
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E92:F92"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="B103:D103"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B103:D103"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="B37:D37"/>
@@ -2637,11 +2538,6 @@
           <t>ÍNDICE DE SISTEMAS</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2649,11 +2545,6 @@
           <t>Un renglón por sistema cotizado · las hojas-formulario leen de aquí</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2826,11 +2717,6 @@
           <t>SISTEMA — Selectivo</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -2845,11 +2731,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2858,8 +2739,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2868,8 +2749,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2878,8 +2759,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2888,8 +2769,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -2897,11 +2778,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -2909,11 +2785,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2922,8 +2793,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2932,8 +2803,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2942,8 +2813,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -2951,11 +2822,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3032,11 +2898,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -3045,8 +2906,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -3066,11 +2927,6 @@
           <t>D) CAPTURA POR DISEÑO — Selectivo</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -3078,11 +2934,6 @@
           <t>Tarima</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3091,8 +2942,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3101,8 +2952,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -3111,8 +2962,8 @@
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3121,8 +2972,8 @@
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3131,8 +2982,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -3141,8 +2992,8 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -3151,8 +3002,8 @@
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -3161,8 +3012,8 @@
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -3170,11 +3021,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -3183,8 +3029,8 @@
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -3193,8 +3039,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -3203,8 +3049,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -3213,8 +3059,8 @@
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -3222,11 +3068,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -3235,8 +3076,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -3245,8 +3086,8 @@
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -3255,8 +3096,8 @@
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -3265,8 +3106,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -3275,8 +3116,8 @@
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -3285,8 +3126,8 @@
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -3295,8 +3136,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -3305,8 +3146,8 @@
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -3314,11 +3155,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -3363,11 +3199,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
@@ -3407,11 +3238,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -3419,11 +3245,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -3432,8 +3253,8 @@
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="C66" s="14" t="n"/>
+      <c r="D66" s="15" t="n"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -3447,8 +3268,8 @@
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="C67" s="14" t="n"/>
+      <c r="D67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -3457,8 +3278,8 @@
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -3467,8 +3288,8 @@
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
-      <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
+      <c r="C69" s="14" t="n"/>
+      <c r="D69" s="15" t="n"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -3481,11 +3302,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="12" t="n"/>
-      <c r="F70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
@@ -3521,11 +3337,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="12" t="n"/>
-      <c r="F77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -3534,8 +3345,8 @@
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="C78" s="14" t="n"/>
+      <c r="D78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -3544,8 +3355,8 @@
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="C79" s="14" t="n"/>
+      <c r="D79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -3554,8 +3365,8 @@
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="C80" s="14" t="n"/>
+      <c r="D80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -3564,8 +3375,8 @@
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="C81" s="14" t="n"/>
+      <c r="D81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -3574,8 +3385,8 @@
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="C82" s="14" t="n"/>
+      <c r="D82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -3584,8 +3395,8 @@
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="C83" s="14" t="n"/>
+      <c r="D83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -3594,8 +3405,8 @@
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="C84" s="14" t="n"/>
+      <c r="D84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -3604,8 +3415,8 @@
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="C85" s="14" t="n"/>
+      <c r="D85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -3613,11 +3424,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="12" t="n"/>
-      <c r="D86" s="12" t="n"/>
-      <c r="E86" s="12" t="n"/>
-      <c r="F86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
@@ -3650,8 +3456,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="63">
@@ -3753,11 +3559,6 @@
           <t>SISTEMA — Dinámico</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -3772,11 +3573,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -3785,8 +3581,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3795,8 +3591,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3805,8 +3601,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3815,8 +3611,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -3824,11 +3620,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -3836,11 +3627,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3849,8 +3635,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3859,8 +3645,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3869,8 +3655,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -3878,11 +3664,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3959,11 +3740,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -3972,8 +3748,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -3993,11 +3769,6 @@
           <t>D) CAPTURA POR DISEÑO — Dinámico</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -4005,11 +3776,6 @@
           <t>Tarima</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -4018,8 +3784,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -4028,8 +3794,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -4038,8 +3804,8 @@
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -4048,8 +3814,8 @@
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -4058,8 +3824,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -4068,8 +3834,8 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4078,8 +3844,8 @@
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -4088,8 +3854,8 @@
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -4097,11 +3863,6 @@
           <t>Configuración del rack</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -4110,8 +3871,8 @@
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -4120,8 +3881,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -4130,8 +3891,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -4140,8 +3901,8 @@
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="15" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Rodillo 2.5/1.9, fácil limpieza, Llantas, Por cálculo</t>
@@ -4155,8 +3916,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Manual / Por cálculo</t>
@@ -4170,8 +3931,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -4180,8 +3941,8 @@
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -4189,11 +3950,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -4202,8 +3958,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -4212,8 +3968,8 @@
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -4222,8 +3978,8 @@
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -4232,8 +3988,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -4241,11 +3997,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -4254,8 +4005,8 @@
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -4264,8 +4015,8 @@
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -4274,8 +4025,8 @@
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -4284,8 +4035,8 @@
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -4294,8 +4045,8 @@
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -4304,8 +4055,8 @@
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -4314,8 +4065,8 @@
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -4324,8 +4075,8 @@
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -4333,11 +4084,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
@@ -4382,11 +4128,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
@@ -4426,11 +4167,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -4438,11 +4174,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -4451,8 +4182,8 @@
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
+      <c r="C74" s="14" t="n"/>
+      <c r="D74" s="15" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -4466,8 +4197,8 @@
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="C75" s="14" t="n"/>
+      <c r="D75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -4476,8 +4207,8 @@
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="C76" s="14" t="n"/>
+      <c r="D76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -4486,8 +4217,8 @@
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="C77" s="14" t="n"/>
+      <c r="D77" s="15" t="n"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -4500,11 +4231,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="12" t="n"/>
-      <c r="D78" s="12" t="n"/>
-      <c r="E78" s="12" t="n"/>
-      <c r="F78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
@@ -4540,11 +4266,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -4553,8 +4274,8 @@
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="C86" s="14" t="n"/>
+      <c r="D86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -4563,8 +4284,8 @@
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="C87" s="14" t="n"/>
+      <c r="D87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -4573,8 +4294,8 @@
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -4583,8 +4304,8 @@
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -4593,8 +4314,8 @@
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -4603,8 +4324,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -4613,8 +4334,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -4623,8 +4344,8 @@
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="C93" s="14" t="n"/>
+      <c r="D93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -4632,11 +4353,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="12" t="n"/>
-      <c r="F94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
@@ -4669,8 +4385,8 @@
         </is>
       </c>
       <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="C100" s="14" t="n"/>
+      <c r="D100" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="73">
@@ -4693,8 +4409,8 @@
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B74:D74"/>
@@ -4729,8 +4445,8 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B90:D90"/>
     <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B90:D90"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="E25:F25"/>
@@ -4782,11 +4498,6 @@
           <t>SISTEMA — Pushback</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -4801,11 +4512,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -4814,8 +4520,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4824,8 +4530,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4834,8 +4540,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -4844,8 +4550,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -4853,11 +4559,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -4865,11 +4566,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4878,8 +4574,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -4888,8 +4584,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4898,8 +4594,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -4907,11 +4603,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -4988,11 +4679,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -5001,8 +4687,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -5022,11 +4708,6 @@
           <t>D) CAPTURA POR DISEÑO — Pushback</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -5034,11 +4715,6 @@
           <t>Tarima</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -5047,8 +4723,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -5057,8 +4733,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -5067,8 +4743,8 @@
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -5077,8 +4753,8 @@
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -5087,8 +4763,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -5097,8 +4773,8 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -5107,8 +4783,8 @@
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -5117,8 +4793,8 @@
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -5126,11 +4802,6 @@
           <t>Configuración del rack</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -5139,8 +4810,8 @@
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -5149,8 +4820,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -5159,8 +4830,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -5169,8 +4840,8 @@
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="15" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Rodillo 2.5/1.9, fácil limpieza, Llantas, Por cálculo</t>
@@ -5184,8 +4855,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Manual / Por cálculo</t>
@@ -5199,8 +4870,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -5209,8 +4880,8 @@
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -5218,11 +4889,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -5231,8 +4897,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -5241,8 +4907,8 @@
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -5251,8 +4917,8 @@
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -5261,8 +4927,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -5270,11 +4936,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -5283,8 +4944,8 @@
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -5293,8 +4954,8 @@
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -5303,8 +4964,8 @@
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -5313,8 +4974,8 @@
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -5323,8 +4984,8 @@
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -5333,8 +4994,8 @@
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -5343,8 +5004,8 @@
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -5353,8 +5014,8 @@
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -5362,11 +5023,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
@@ -5411,11 +5067,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
@@ -5455,11 +5106,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -5467,11 +5113,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -5480,8 +5121,8 @@
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
+      <c r="C74" s="14" t="n"/>
+      <c r="D74" s="15" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -5495,8 +5136,8 @@
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
+      <c r="C75" s="14" t="n"/>
+      <c r="D75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -5505,8 +5146,8 @@
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="C76" s="14" t="n"/>
+      <c r="D76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -5515,8 +5156,8 @@
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="C77" s="14" t="n"/>
+      <c r="D77" s="15" t="n"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -5529,11 +5170,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="12" t="n"/>
-      <c r="D78" s="12" t="n"/>
-      <c r="E78" s="12" t="n"/>
-      <c r="F78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
@@ -5569,11 +5205,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -5582,8 +5213,8 @@
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="C86" s="14" t="n"/>
+      <c r="D86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -5592,8 +5223,8 @@
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="C87" s="14" t="n"/>
+      <c r="D87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -5602,8 +5233,8 @@
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -5612,8 +5243,8 @@
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -5622,8 +5253,8 @@
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -5632,8 +5263,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -5642,8 +5273,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -5652,8 +5283,8 @@
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="C93" s="14" t="n"/>
+      <c r="D93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -5661,11 +5292,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="12" t="n"/>
-      <c r="F94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
@@ -5698,8 +5324,8 @@
         </is>
       </c>
       <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
+      <c r="C100" s="14" t="n"/>
+      <c r="D100" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="73">
@@ -5722,8 +5348,8 @@
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B74:D74"/>
@@ -5758,8 +5384,8 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B90:D90"/>
     <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B90:D90"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="E25:F25"/>
@@ -5811,11 +5437,6 @@
           <t>SISTEMA — Drive in</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -5830,11 +5451,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -5843,8 +5459,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5853,8 +5469,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -5863,8 +5479,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -5873,8 +5489,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -5882,11 +5498,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -5894,11 +5505,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5907,8 +5513,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -5917,8 +5523,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5927,8 +5533,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -5936,11 +5542,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -6017,11 +5618,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -6030,8 +5626,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -6051,11 +5647,6 @@
           <t>D) CAPTURA POR DISEÑO — Drive in</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -6063,11 +5654,6 @@
           <t>Tarima</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -6076,8 +5662,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -6086,8 +5672,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -6096,8 +5682,8 @@
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -6106,8 +5692,8 @@
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -6116,8 +5702,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -6126,8 +5712,8 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -6136,8 +5722,8 @@
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -6146,8 +5732,8 @@
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -6155,11 +5741,6 @@
           <t>Configuración del rack</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -6168,8 +5749,8 @@
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -6178,8 +5759,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -6188,8 +5769,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -6197,11 +5778,6 @@
           <t>Montacargas</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -6210,8 +5786,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Medidas / Modelo</t>
@@ -6225,8 +5801,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -6235,8 +5811,8 @@
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -6245,8 +5821,8 @@
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -6255,8 +5831,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -6264,11 +5840,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -6277,8 +5848,8 @@
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -6287,8 +5858,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -6297,8 +5868,8 @@
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -6307,8 +5878,8 @@
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -6316,11 +5887,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="12" t="n"/>
-      <c r="F52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -6329,8 +5895,8 @@
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -6339,8 +5905,8 @@
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -6349,8 +5915,8 @@
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -6359,8 +5925,8 @@
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -6369,8 +5935,8 @@
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -6379,8 +5945,8 @@
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -6389,8 +5955,8 @@
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="C59" s="14" t="n"/>
+      <c r="D59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -6399,8 +5965,8 @@
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -6408,11 +5974,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
@@ -6457,11 +6018,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
@@ -6501,11 +6057,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -6513,11 +6064,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="12" t="n"/>
-      <c r="F75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -6526,8 +6072,8 @@
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
+      <c r="C76" s="14" t="n"/>
+      <c r="D76" s="15" t="n"/>
       <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -6541,8 +6087,8 @@
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="C77" s="14" t="n"/>
+      <c r="D77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -6551,8 +6097,8 @@
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="C78" s="14" t="n"/>
+      <c r="D78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -6561,8 +6107,8 @@
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="C79" s="14" t="n"/>
+      <c r="D79" s="15" t="n"/>
       <c r="E79" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -6575,11 +6121,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
@@ -6615,11 +6156,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="12" t="n"/>
-      <c r="D87" s="12" t="n"/>
-      <c r="E87" s="12" t="n"/>
-      <c r="F87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -6628,8 +6164,8 @@
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -6638,8 +6174,8 @@
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -6648,8 +6184,8 @@
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -6658,8 +6194,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -6668,8 +6204,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -6678,8 +6214,8 @@
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="C93" s="14" t="n"/>
+      <c r="D93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -6688,8 +6224,8 @@
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
+      <c r="C94" s="14" t="n"/>
+      <c r="D94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -6698,8 +6234,8 @@
         </is>
       </c>
       <c r="B95" s="8" t="n"/>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
+      <c r="C95" s="14" t="n"/>
+      <c r="D95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -6707,11 +6243,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B96" s="12" t="n"/>
-      <c r="C96" s="12" t="n"/>
-      <c r="D96" s="12" t="n"/>
-      <c r="E96" s="12" t="n"/>
-      <c r="F96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
@@ -6744,8 +6275,8 @@
         </is>
       </c>
       <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
+      <c r="C102" s="14" t="n"/>
+      <c r="D102" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="74">
@@ -6766,8 +6297,8 @@
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E79:F79"/>
@@ -6812,9 +6343,9 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="E76:F76"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="A61:F61"/>
@@ -6858,11 +6389,6 @@
           <t>SISTEMA — Cantiléver</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -6877,11 +6403,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -6890,8 +6411,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6900,8 +6421,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6910,8 +6431,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -6920,8 +6441,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -6929,11 +6450,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -6941,11 +6457,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6954,8 +6465,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6964,8 +6475,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6974,8 +6485,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6983,11 +6494,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -7064,11 +6570,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -7077,8 +6578,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -7098,11 +6599,6 @@
           <t>D) CAPTURA POR DISEÑO — Cantiléver</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -7110,11 +6606,6 @@
           <t>Carga / producto</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -7123,8 +6614,8 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -7133,8 +6624,8 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -7143,8 +6634,8 @@
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -7153,8 +6644,8 @@
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -7163,8 +6654,8 @@
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -7172,21 +6663,16 @@
           <t>Configuración del rack (cantiléver)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>¿Góndola sencilla o doble?</t>
+          <t>¿Tipo de góndola?</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -7194,11 +6680,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -7207,8 +6688,8 @@
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -7217,8 +6698,8 @@
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -7227,8 +6708,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -7237,8 +6718,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -7246,11 +6727,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -7259,8 +6735,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -7269,8 +6745,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -7279,8 +6755,8 @@
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -7289,8 +6765,8 @@
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -7299,8 +6775,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -7309,8 +6785,8 @@
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -7319,8 +6795,8 @@
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -7329,8 +6805,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -7338,11 +6814,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
@@ -7387,11 +6858,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
@@ -7431,11 +6897,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -7443,11 +6904,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="12" t="n"/>
-      <c r="F64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -7456,8 +6912,8 @@
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
+      <c r="C65" s="14" t="n"/>
+      <c r="D65" s="15" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -7471,8 +6927,8 @@
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
+      <c r="C66" s="14" t="n"/>
+      <c r="D66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -7481,8 +6937,8 @@
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
+      <c r="C67" s="14" t="n"/>
+      <c r="D67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -7491,8 +6947,8 @@
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="15" t="n"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -7505,11 +6961,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
@@ -7545,11 +6996,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -7558,8 +7004,8 @@
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="C77" s="14" t="n"/>
+      <c r="D77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -7568,8 +7014,8 @@
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="C78" s="14" t="n"/>
+      <c r="D78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -7578,8 +7024,8 @@
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="C79" s="14" t="n"/>
+      <c r="D79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -7588,8 +7034,8 @@
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="C80" s="14" t="n"/>
+      <c r="D80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -7598,8 +7044,8 @@
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
+      <c r="C81" s="14" t="n"/>
+      <c r="D81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -7608,8 +7054,8 @@
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="C82" s="14" t="n"/>
+      <c r="D82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -7618,8 +7064,8 @@
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="C83" s="14" t="n"/>
+      <c r="D83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -7628,8 +7074,8 @@
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="C84" s="14" t="n"/>
+      <c r="D84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -7637,11 +7083,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
@@ -7674,8 +7115,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="62">
@@ -7776,11 +7217,6 @@
           <t>SISTEMA — Mezzanine</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -7795,11 +7231,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -7808,8 +7239,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7818,8 +7249,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -7828,8 +7259,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -7838,8 +7269,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -7847,11 +7278,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -7859,11 +7285,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7872,8 +7293,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -7882,8 +7303,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -7892,8 +7313,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -7901,11 +7322,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -7982,11 +7398,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -7995,8 +7406,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -8016,11 +7427,6 @@
           <t>D) CAPTURA POR DISEÑO — Mezzanine</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -8028,11 +7434,6 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -8040,11 +7441,6 @@
           <t>Productos (un renglón por producto)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -8132,11 +7528,6 @@
           <t>Configuración del entrepiso</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -8145,8 +7536,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>default 2.4 m</t>
@@ -8160,8 +7551,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -8170,8 +7561,8 @@
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -8180,8 +7571,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -8190,8 +7581,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Rejilla Irving / MDF</t>
@@ -8205,8 +7596,8 @@
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -8215,8 +7606,8 @@
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -8225,8 +7616,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -8235,8 +7626,8 @@
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -8245,8 +7636,8 @@
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -8255,8 +7646,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -8265,8 +7656,8 @@
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -8274,11 +7665,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -8287,8 +7673,8 @@
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -8297,8 +7683,8 @@
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -8307,8 +7693,8 @@
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -8316,11 +7702,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -8329,8 +7710,8 @@
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -8339,8 +7720,8 @@
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -8349,8 +7730,8 @@
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -8359,8 +7740,8 @@
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
+      <c r="C59" s="14" t="n"/>
+      <c r="D59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -8369,8 +7750,8 @@
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -8379,8 +7760,8 @@
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="C61" s="14" t="n"/>
+      <c r="D61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -8388,11 +7769,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
@@ -8437,11 +7813,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
@@ -8481,11 +7852,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -8493,11 +7859,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -8506,8 +7867,8 @@
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
+      <c r="C77" s="14" t="n"/>
+      <c r="D77" s="15" t="n"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -8521,8 +7882,8 @@
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
+      <c r="C78" s="14" t="n"/>
+      <c r="D78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -8531,8 +7892,8 @@
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
+      <c r="C79" s="14" t="n"/>
+      <c r="D79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -8541,8 +7902,8 @@
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
+      <c r="C80" s="14" t="n"/>
+      <c r="D80" s="15" t="n"/>
       <c r="E80" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -8555,11 +7916,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
@@ -8595,11 +7951,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -8608,8 +7959,8 @@
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -8618,8 +7969,8 @@
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -8628,8 +7979,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -8638,8 +7989,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -8648,8 +7999,8 @@
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
+      <c r="C93" s="14" t="n"/>
+      <c r="D93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -8658,8 +8009,8 @@
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
+      <c r="C94" s="14" t="n"/>
+      <c r="D94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -8668,8 +8019,8 @@
         </is>
       </c>
       <c r="B95" s="8" t="n"/>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
+      <c r="C95" s="14" t="n"/>
+      <c r="D95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -8678,8 +8029,8 @@
         </is>
       </c>
       <c r="B96" s="8" t="n"/>
-      <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="C96" s="14" t="n"/>
+      <c r="D96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -8687,11 +8038,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B97" s="12" t="n"/>
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="12" t="n"/>
-      <c r="F97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
@@ -8724,8 +8070,8 @@
         </is>
       </c>
       <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
+      <c r="C103" s="14" t="n"/>
+      <c r="D103" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="68">
@@ -8833,11 +8179,6 @@
           <t>SISTEMA — Carton flow</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -8852,11 +8193,6 @@
           <t>Identificación</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -8865,8 +8201,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -8875,8 +8211,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -8885,8 +8221,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -8895,8 +8231,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -8904,11 +8240,6 @@
           <t>MÉTODO DE CAPTURA</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -8916,11 +8247,6 @@
           <t>A) Cotización o pedido anterior</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -8929,8 +8255,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -8939,8 +8265,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -8949,8 +8275,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -8958,11 +8284,6 @@
           <t>B) Listado de piezas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -9039,11 +8360,6 @@
           <t>C) Planos / diseño de cliente</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -9052,8 +8368,8 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>usar adjuntos de la cotización</t>
@@ -9073,11 +8389,6 @@
           <t>D) CAPTURA POR DISEÑO — Carton flow</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -9085,11 +8396,6 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -9097,11 +8403,6 @@
           <t>Productos (un renglón por producto)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -9189,11 +8490,6 @@
           <t>Configuración del rack (carton flow)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -9202,8 +8498,8 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -9212,8 +8508,8 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -9222,8 +8518,8 @@
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -9232,8 +8528,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="15" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Rodillo de 3/4 / Rodajas</t>
@@ -9247,8 +8543,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="15" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Manual / Por cálculo</t>
@@ -9261,11 +8557,6 @@
           <t>Área disponible / pasillos</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -9274,8 +8565,8 @@
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -9284,8 +8575,8 @@
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -9294,8 +8585,8 @@
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -9303,11 +8594,6 @@
           <t>Criterios para configuración de niveles</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -9316,8 +8602,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -9326,8 +8612,8 @@
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -9336,8 +8622,8 @@
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -9346,8 +8632,8 @@
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -9356,8 +8642,8 @@
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -9366,8 +8652,8 @@
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -9375,11 +8661,6 @@
           <t>Elementos de seguridad — Listado de piezas</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
@@ -9424,11 +8705,6 @@
           <t>Piezas especiales</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
@@ -9468,11 +8744,6 @@
           <t>DATOS COMUNES DEL SISTEMA (siempre)</t>
         </is>
       </c>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -9480,11 +8751,6 @@
           <t>Acabado</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -9493,8 +8759,8 @@
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
+      <c r="C70" s="14" t="n"/>
+      <c r="D70" s="15" t="n"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Pintado / Galv. frío / Galv. caliente / Pregalvanizado</t>
@@ -9508,8 +8774,8 @@
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
-      <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
+      <c r="C71" s="14" t="n"/>
+      <c r="D71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -9518,8 +8784,8 @@
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -9528,8 +8794,8 @@
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
+      <c r="C73" s="14" t="n"/>
+      <c r="D73" s="15" t="n"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
           <t>solo galv. frío/caliente</t>
@@ -9542,11 +8808,6 @@
           <t>Colores por pieza</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
@@ -9582,11 +8843,6 @@
           <t>Servicios y consideraciones</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -9595,8 +8851,8 @@
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
+      <c r="C82" s="14" t="n"/>
+      <c r="D82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -9605,8 +8861,8 @@
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
+      <c r="C83" s="14" t="n"/>
+      <c r="D83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -9615,8 +8871,8 @@
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
+      <c r="C84" s="14" t="n"/>
+      <c r="D84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -9625,8 +8881,8 @@
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
+      <c r="C85" s="14" t="n"/>
+      <c r="D85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -9635,8 +8891,8 @@
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
+      <c r="C86" s="14" t="n"/>
+      <c r="D86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -9645,8 +8901,8 @@
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
+      <c r="C87" s="14" t="n"/>
+      <c r="D87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -9655,8 +8911,8 @@
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -9665,8 +8921,8 @@
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -9674,11 +8930,6 @@
           <t>Proveedores externos</t>
         </is>
       </c>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="12" t="n"/>
-      <c r="D90" s="12" t="n"/>
-      <c r="E90" s="12" t="n"/>
-      <c r="F90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
@@ -9711,8 +8962,8 @@
         </is>
       </c>
       <c r="B96" s="8" t="n"/>
-      <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
+      <c r="C96" s="14" t="n"/>
+      <c r="D96" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="61">

--- a/templates/FDI_Master.xlsx
+++ b/templates/FDI_Master.xlsx
@@ -8532,7 +8532,7 @@
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Rodillo de 3/4 / Rodajas</t>
+          <t>Rodillo de 3/4 / Rodajas / Por diseño</t>
         </is>
       </c>
     </row>

--- a/templates/FDI_Master.xlsx
+++ b/templates/FDI_Master.xlsx
@@ -17,6 +17,7 @@
     <sheet name="MEZ_S01_Form" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="CFL_S01_Form" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="MZL_S01_Form" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FDI_Table_Config" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -285,543 +286,730 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tbl009" displayName="tbl009" ref="A79:B83" headerRowCount="1">
-  <autoFilter ref="A79:B83"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblTarimas_DIN" displayName="tblTarimas_DIN" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl010" displayName="tbl010" ref="A95:B98" headerRowCount="1">
-  <autoFilter ref="A95:B98"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblProductos_DIN" displayName="tblProductos_DIN" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl011" displayName="tbl011" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblElementosSeguridad_DIN" displayName="tblElementosSeguridad_DIN" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl012" displayName="tbl012" ref="A60:C64" headerRowCount="1">
-  <autoFilter ref="A60:C64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPiezasEspeciales_DIN" displayName="tblPiezasEspeciales_DIN" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl013" displayName="tbl013" ref="A67:C70" headerRowCount="1">
-  <autoFilter ref="A67:C70"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tblColores_DIN" displayName="tblColores_DIN" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
+  <tableColumns count="2">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl014" displayName="tbl014" ref="A79:B83" headerRowCount="1">
-  <autoFilter ref="A79:B83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblProveedoresExternos_DIN" displayName="tblProveedoresExternos_DIN" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl015" displayName="tbl015" ref="A95:B98" headerRowCount="1">
-  <autoFilter ref="A95:B98"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblPiezas_PBK" displayName="tblPiezas_PBK" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl016" displayName="tbl016" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblTarimas_PBK" displayName="tblTarimas_PBK" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl017" displayName="tbl017" ref="A62:C66" headerRowCount="1">
-  <autoFilter ref="A62:C66"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblProductos_PBK" displayName="tblProductos_PBK" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl018" displayName="tbl018" ref="A69:C72" headerRowCount="1">
-  <autoFilter ref="A69:C72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblElementosSeguridad_PBK" displayName="tblElementosSeguridad_PBK" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl001" displayName="tbl001" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblPiezas_SEL" displayName="tblPiezas_SEL" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl019" displayName="tbl019" ref="A81:B85" headerRowCount="1">
-  <autoFilter ref="A81:B85"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tblPiezasEspeciales_PBK" displayName="tblPiezasEspeciales_PBK" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl020" displayName="tbl020" ref="A97:B100" headerRowCount="1">
-  <autoFilter ref="A97:B100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tblColores_PBK" displayName="tblColores_PBK" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl021" displayName="tbl021" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tblProveedoresExternos_PBK" displayName="tblProveedoresExternos_PBK" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
+  <tableColumns count="2">
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl022" displayName="tbl022" ref="A51:C55" headerRowCount="1">
-  <autoFilter ref="A51:C55"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tblPiezas_DRV" displayName="tblPiezas_DRV" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl023" displayName="tbl023" ref="A58:C61" headerRowCount="1">
-  <autoFilter ref="A58:C61"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tblTarimas_DRV" displayName="tblTarimas_DRV" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl024" displayName="tbl024" ref="A70:B74" headerRowCount="1">
-  <autoFilter ref="A70:B74"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tblProductos_DRV" displayName="tblProductos_DRV" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl025" displayName="tbl025" ref="A86:B89" headerRowCount="1">
-  <autoFilter ref="A86:B89"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tblElementosSeguridad_DRV" displayName="tblElementosSeguridad_DRV" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl026" displayName="tbl026" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tblPiezasEspeciales_DRV" displayName="tblPiezasEspeciales_DRV" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl027" displayName="tbl027" ref="A30:F36" headerRowCount="1">
-  <autoFilter ref="A30:F36"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Tipo de producto"/>
-    <tableColumn id="2" name="Largo"/>
-    <tableColumn id="3" name="Ancho"/>
-    <tableColumn id="4" name="Alto"/>
-    <tableColumn id="5" name="Peso/pieza"/>
-    <tableColumn id="6" name="Cant./nivel"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tblColores_DRV" displayName="tblColores_DRV" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
+  <tableColumns count="2">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl028" displayName="tbl028" ref="A63:C67" headerRowCount="1">
-  <autoFilter ref="A63:C67"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tblProveedoresExternos_DRV" displayName="tblProveedoresExternos_DRV" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
+  <tableColumns count="2">
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl002" displayName="tbl002" ref="A52:C56" headerRowCount="1">
-  <autoFilter ref="A52:C56"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblTarimas_SEL" displayName="tblTarimas_SEL" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl029" displayName="tbl029" ref="A70:C73" headerRowCount="1">
-  <autoFilter ref="A70:C73"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tblPiezas_CAN" displayName="tblPiezas_CAN" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl030" displayName="tbl030" ref="A82:B86" headerRowCount="1">
-  <autoFilter ref="A82:B86"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tblTarimas_CAN" displayName="tblTarimas_CAN" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tbl031" displayName="tbl031" ref="A98:B101" headerRowCount="1">
-  <autoFilter ref="A98:B101"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tblProductos_CAN" displayName="tblProductos_CAN" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="tbl032" displayName="tbl032" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="tblElementosSeguridad_CAN" displayName="tblElementosSeguridad_CAN" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="tbl033" displayName="tbl033" ref="A30:F36" headerRowCount="1">
-  <autoFilter ref="A30:F36"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Tipo de producto"/>
-    <tableColumn id="2" name="Largo"/>
-    <tableColumn id="3" name="Ancho"/>
-    <tableColumn id="4" name="Alto"/>
-    <tableColumn id="5" name="Peso/pieza"/>
-    <tableColumn id="6" name="Cant./nivel"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="tblPiezasEspeciales_CAN" displayName="tblPiezasEspeciales_CAN" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="tbl034" displayName="tbl034" ref="A56:C60" headerRowCount="1">
-  <autoFilter ref="A56:C60"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="tblColores_CAN" displayName="tblColores_CAN" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
+  <tableColumns count="2">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="tbl035" displayName="tbl035" ref="A63:C66" headerRowCount="1">
-  <autoFilter ref="A63:C66"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="tblProveedoresExternos_CAN" displayName="tblProveedoresExternos_CAN" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
+  <tableColumns count="2">
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="tbl036" displayName="tbl036" ref="A75:B79" headerRowCount="1">
-  <autoFilter ref="A75:B79"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="tblPiezas_MEZ" displayName="tblPiezas_MEZ" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="tbl037" displayName="tbl037" ref="A91:B94" headerRowCount="1">
-  <autoFilter ref="A91:B94"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="tblTarimas_MEZ" displayName="tblTarimas_MEZ" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="tbl038" displayName="tbl038" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="tblProductos_MEZ" displayName="tblProductos_MEZ" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tbl003" displayName="tbl003" ref="A59:C62" headerRowCount="1">
-  <autoFilter ref="A59:C62"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblProductos_SEL" displayName="tblProductos_SEL" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="tbl039" displayName="tbl039" ref="A49:F53" headerRowCount="1">
-  <autoFilter ref="A49:F53"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Tipo de producto"/>
-    <tableColumn id="2" name="Largo"/>
-    <tableColumn id="3" name="Ancho"/>
-    <tableColumn id="4" name="Alto"/>
-    <tableColumn id="5" name="Peso/pieza"/>
-    <tableColumn id="6" name="Cant./nivel"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="tblElementosSeguridad_MEZ" displayName="tblElementosSeguridad_MEZ" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tbl040" displayName="tbl040" ref="A57:G61" headerRowCount="1">
-  <autoFilter ref="A57:G61"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Peso"/>
-    <tableColumn id="2" name="Alto"/>
-    <tableColumn id="3" name="Frente"/>
-    <tableColumn id="4" name="Fondo"/>
-    <tableColumn id="5" name="Huella"/>
-    <tableColumn id="6" name="Exc. frente"/>
-    <tableColumn id="7" name="Exc. fondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tblPiezasEspeciales_MEZ" displayName="tblPiezasEspeciales_MEZ" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="tbl041" displayName="tbl041" ref="A75:C79" headerRowCount="1">
-  <autoFilter ref="A75:C79"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="tblColores_MEZ" displayName="tblColores_MEZ" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
+  <tableColumns count="2">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table43.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="tbl042" displayName="tbl042" ref="A82:C85" headerRowCount="1">
-  <autoFilter ref="A82:C85"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="tblProveedoresExternos_MEZ" displayName="tblProveedoresExternos_MEZ" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
+  <tableColumns count="2">
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table44.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="tbl043" displayName="tbl043" ref="A94:B98" headerRowCount="1">
-  <autoFilter ref="A94:B98"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="tblPiezas_CFL" displayName="tblPiezas_CFL" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tbl044" displayName="tbl044" ref="A110:B113" headerRowCount="1">
-  <autoFilter ref="A110:B113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tblTarimas_CFL" displayName="tblTarimas_CFL" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="tblProductos_CFL" displayName="tblProductos_CFL" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="tblElementosSeguridad_CFL" displayName="tblElementosSeguridad_CFL" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table48.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="tblPiezasEspeciales_CFL" displayName="tblPiezasEspeciales_CFL" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table49.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="tblColores_CFL" displayName="tblColores_CFL" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tbl004" displayName="tbl004" ref="A71:B75" headerRowCount="1">
-  <autoFilter ref="A71:B75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblElementosSeguridad_SEL" displayName="tblElementosSeguridad_SEL" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table50.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="tblProveedoresExternos_CFL" displayName="tblProveedoresExternos_CFL" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Color"/>
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table51.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="tblPiezas_MZL" displayName="tblPiezas_MZL" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table52.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="tblTarimas_MZL" displayName="tblTarimas_MZL" ref="O4:U29" headerRowCount="1">
+  <autoFilter ref="O4:U29"/>
+  <tableColumns count="7">
+    <tableColumn id="15" name="Peso"/>
+    <tableColumn id="16" name="Alto"/>
+    <tableColumn id="17" name="Frente"/>
+    <tableColumn id="18" name="Fondo"/>
+    <tableColumn id="19" name="Huella"/>
+    <tableColumn id="20" name="ExcedenteFrente"/>
+    <tableColumn id="21" name="ExcedenteFondo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table53.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="tblProductos_MZL" displayName="tblProductos_MZL" ref="I32:N57" headerRowCount="1">
+  <autoFilter ref="I32:N57"/>
+  <tableColumns count="6">
+    <tableColumn id="9" name="TipoProducto"/>
+    <tableColumn id="10" name="LargoProducto"/>
+    <tableColumn id="11" name="AnchoProducto"/>
+    <tableColumn id="12" name="AltoProducto"/>
+    <tableColumn id="13" name="PesoProducto"/>
+    <tableColumn id="14" name="CantidadPorNivel"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table54.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="tblElementosSeguridad_MZL" displayName="tblElementosSeguridad_MZL" ref="P32:R57" headerRowCount="1">
+  <autoFilter ref="P32:R57"/>
+  <tableColumns count="3">
+    <tableColumn id="16" name="Pieza"/>
+    <tableColumn id="17" name="Cantidad"/>
+    <tableColumn id="18" name="Comentario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="tblPiezasEspeciales_MZL" displayName="tblPiezasEspeciales_MZL" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="tblColores_MZL" displayName="tblColores_MZL" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
+  <tableColumns count="2">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="tblProveedoresExternos_MZL" displayName="tblProveedoresExternos_MZL" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
+  <tableColumns count="2">
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tbl005" displayName="tbl005" ref="A87:B90" headerRowCount="1">
-  <autoFilter ref="A87:B90"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Proveedor"/>
-    <tableColumn id="2" name="Alcance"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblPiezasEspeciales_SEL" displayName="tblPiezasEspeciales_SEL" ref="T32:V57" headerRowCount="1">
+  <autoFilter ref="T32:V57"/>
+  <tableColumns count="3">
+    <tableColumn id="20" name="Pieza"/>
+    <tableColumn id="21" name="Cantidad"/>
+    <tableColumn id="22" name="Comentario"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl006" displayName="tbl006" ref="A16:E22" headerRowCount="1">
-  <autoFilter ref="A16:E22"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Código"/>
-    <tableColumn id="2" name="Descripción"/>
-    <tableColumn id="3" name="Cantidad"/>
-    <tableColumn id="4" name="Unidad"/>
-    <tableColumn id="5" name="Notas"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblColores_SEL" displayName="tblColores_SEL" ref="I60:J85" headerRowCount="1">
+  <autoFilter ref="I60:J85"/>
+  <tableColumns count="2">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Color"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl007" displayName="tbl007" ref="A60:C64" headerRowCount="1">
-  <autoFilter ref="A60:C64"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblProveedoresExternos_SEL" displayName="tblProveedoresExternos_SEL" ref="L60:M85" headerRowCount="1">
+  <autoFilter ref="L60:M85"/>
+  <tableColumns count="2">
+    <tableColumn id="12" name="Proveedor"/>
+    <tableColumn id="13" name="Alcance"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl008" displayName="tbl008" ref="A67:C70" headerRowCount="1">
-  <autoFilter ref="A67:C70"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Pieza"/>
-    <tableColumn id="2" name="Cantidad"/>
-    <tableColumn id="3" name="Comentario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tblPiezas_DIN" displayName="tblPiezas_DIN" ref="I4:M29" headerRowCount="1">
+  <autoFilter ref="I4:M29"/>
+  <tableColumns count="5">
+    <tableColumn id="9" name="Pieza"/>
+    <tableColumn id="10" name="Comentarios"/>
+    <tableColumn id="11" name="Cantidad"/>
+    <tableColumn id="12" name="Unidad"/>
+    <tableColumn id="13" name="Notas"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1422,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:V115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1619,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1453,6 +1655,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1494,6 +1756,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -1614,6 +1877,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -1696,6 +1960,66 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="15" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1922,6 +2246,7 @@
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
@@ -1999,6 +2324,26 @@
       <c r="E60" s="10" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n"/>
@@ -2009,6 +2354,7 @@
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
@@ -2157,6 +2503,7 @@
       <c r="B79" s="10" t="n"/>
       <c r="C79" s="10" t="n"/>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
@@ -2515,6 +2862,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FDI Excel layout JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:V"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:U29","headers":["Peso","Alto","Frente","Fondo","Huella","ExcedenteFrente","ExcedenteFondo"],"aliases":[["Peso","PesoTarima"],["Alto","AltoTarima"],["Frente","FrenteTarima"],["Fondo","FondoTarima"],["Huella","HuellaTarima"],["ExcedenteFrente","Excedente frente"],["ExcedenteFondo","Excedente fondo"]],"previewRanges":{"MZL":"A57:G61"}},"productos":{"baseName":"tblProductos","range":"I32:N57","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"P32:R57","headers":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"T32:V57","headers":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"I60:J85","headers":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"L60:M85","headers":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2700,7 +3075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2709,6 +3084,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2731,6 +3120,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2772,6 +3221,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -2892,6 +3342,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -2974,6 +3425,66 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="15" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3193,6 +3704,7 @@
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
@@ -3221,6 +3733,26 @@
       <c r="A60" s="10" t="n"/>
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n"/>
@@ -3232,6 +3764,7 @@
       <c r="B62" s="10" t="n"/>
       <c r="C62" s="10" t="n"/>
     </row>
+    <row r="63"/>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
@@ -3331,6 +3864,7 @@
       <c r="A75" s="10" t="n"/>
       <c r="B75" s="10" t="n"/>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
@@ -3526,12 +4060,14 @@
     <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="5">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3542,7 +4078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3551,6 +4087,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3573,6 +4123,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -3614,6 +4224,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -3734,6 +4345,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -3816,6 +4428,66 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="15" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -4101,6 +4773,26 @@
           <t>Comentario</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n"/>
@@ -4122,6 +4814,7 @@
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
@@ -4161,6 +4854,7 @@
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="10" t="n"/>
     </row>
+    <row r="71"/>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4260,6 +4954,7 @@
       <c r="A83" s="10" t="n"/>
       <c r="B83" s="10" t="n"/>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
@@ -4465,12 +5160,14 @@
     <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="5">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4481,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4490,6 +5187,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4512,6 +5223,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -4553,6 +5324,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -4673,6 +5445,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -4755,6 +5528,66 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="15" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -5040,6 +5873,26 @@
           <t>Comentario</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n"/>
@@ -5061,6 +5914,7 @@
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
@@ -5100,6 +5954,7 @@
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="10" t="n"/>
     </row>
+    <row r="71"/>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -5199,6 +6054,7 @@
       <c r="A83" s="10" t="n"/>
       <c r="B83" s="10" t="n"/>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
@@ -5404,12 +6260,14 @@
     <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="5">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5420,7 +6278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5429,6 +6287,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5451,6 +6323,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -5492,6 +6424,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -5612,6 +6545,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -5694,6 +6628,66 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="15" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -5967,6 +6961,26 @@
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="14" t="n"/>
       <c r="D60" s="15" t="n"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -6012,6 +7026,7 @@
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
@@ -6051,6 +7066,7 @@
       <c r="B72" s="10" t="n"/>
       <c r="C72" s="10" t="n"/>
     </row>
+    <row r="73"/>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
@@ -6356,12 +7372,14 @@
     <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="5">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6372,7 +7390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6381,6 +7399,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6403,6 +7435,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -6444,6 +7536,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -6564,6 +7657,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -6646,6 +7740,66 @@
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="15" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -6852,6 +8006,7 @@
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
@@ -6885,12 +8040,33 @@
       <c r="A60" s="10" t="n"/>
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n"/>
       <c r="B61" s="10" t="n"/>
       <c r="C61" s="10" t="n"/>
     </row>
+    <row r="62"/>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
@@ -6990,6 +8166,7 @@
       <c r="A74" s="10" t="n"/>
       <c r="B74" s="10" t="n"/>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
@@ -7184,12 +8361,14 @@
     <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="5">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7200,7 +8379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7209,6 +8388,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -7231,6 +8424,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -7272,6 +8525,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -7392,6 +8646,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -7489,6 +8744,66 @@
       <c r="D32" s="10" t="n"/>
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
@@ -7522,6 +8837,7 @@
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -7752,6 +9068,26 @@
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="14" t="n"/>
       <c r="D60" s="15" t="n"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -7807,6 +9143,7 @@
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="10" t="n"/>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
@@ -7846,6 +9183,7 @@
       <c r="B73" s="10" t="n"/>
       <c r="C73" s="10" t="n"/>
     </row>
+    <row r="74"/>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
@@ -8145,13 +9483,14 @@
     <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="6">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8162,7 +9501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8171,6 +9510,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8193,6 +9546,66 @@
           <t>Identificación</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Frente</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Huella</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ExcedenteFrente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ExcedenteFondo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -8234,6 +9647,7 @@
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -8354,6 +9768,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -8451,6 +9866,66 @@
       <c r="D32" s="10" t="n"/>
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
@@ -8484,6 +9959,7 @@
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -8698,7 +10174,28 @@
       <c r="A60" s="10" t="n"/>
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
-    </row>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
@@ -8738,6 +10235,7 @@
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
     </row>
+    <row r="67"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -8837,6 +10335,7 @@
       <c r="A79" s="10" t="n"/>
       <c r="B79" s="10" t="n"/>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
@@ -9030,13 +10529,14 @@
     <mergeCell ref="B86:D86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="6">
+  <tableParts count="7">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/templates/FDI_Master.xlsx
+++ b/templates/FDI_Master.xlsx
@@ -5046,7 +5046,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:V"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"previewHeaders":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:U29","headers":["Peso","Alto","Frente","Fondo","Huella","ExcedenteFrente","ExcedenteFondo"],"previewHeaders":["Peso","Alto","Frente","Fondo","Huella","Exc. frente","Exc. fondo"],"aliases":[["Peso","PesoTarima"],["Alto","AltoTarima"],["Frente","FrenteTarima"],["Fondo","FondoTarima"],["Huella","HuellaTarima"],["ExcedenteFrente","Excedente frente"],["ExcedenteFondo","Excedente fondo"]],"previewRanges":{"SEL":"A29:G36","DIN":"A29:G36","PBK":"A29:G36","DRV":"A29:G36","MZL":"A57:G61"}},"productos":{"baseName":"tblProductos","range":"I32:N57","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"previewHeaders":["Tipo","Largo","Ancho","Alto","Peso","Cant./nivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"P32:R57","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"T32:V57","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"I60:J85","headers":["Pieza","Color"],"previewHeaders":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"L60:M85","headers":["Proveedor","Alcance"],"previewHeaders":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
+          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:V"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"previewHeaders":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:U29","headers":["Peso","Alto","Frente","Fondo","Huella","ExcedenteFrente","ExcedenteFondo"],"previewHeaders":["Peso","Alto","Frente","Fondo","Huella","Exc. frente","Exc. fondo"],"aliases":[["Peso","PesoTarima","Pesotarima","Peso tarima"],["Alto","AltoTarima","Altotarima","Alto tarima"],["Frente","FrenteTarima","Frentetarima","Frente tarima"],["Fondo","FondoTarima","Fondotarima","Fondo tarima"],["Huella","HuellaTarima","Huellatarima","Huella tarima"],["ExcedenteFrente","Excedente frente","Excedentefrente"],["ExcedenteFondo","Excedente fondo","Excedentefondo"]],"previewRanges":{"SEL":"A29:G36","DIN":"A29:G36","PBK":"A29:G36","DRV":"A29:G36","MZL":"A57:G61"}},"productos":{"baseName":"tblProductos","range":"I32:N57","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"previewHeaders":["Tipo","Largo","Ancho","Alto","Peso","Cant./nivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"P32:R57","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"T32:V57","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"I60:J85","headers":["Pieza","Color"],"previewHeaders":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"L60:M85","headers":["Proveedor","Alcance"],"previewHeaders":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
         </is>
       </c>
     </row>

--- a/templates/FDI_Master.xlsx
+++ b/templates/FDI_Master.xlsx
@@ -311,61 +311,61 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblProductos_DIN" displayName="tblProductos_DIN" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblProductos_DIN" displayName="tblProductos_DIN" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblElementosSeguridad_DIN" displayName="tblElementosSeguridad_DIN" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblElementosSeguridad_DIN" displayName="tblElementosSeguridad_DIN" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPiezasEspeciales_DIN" displayName="tblPiezasEspeciales_DIN" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblPiezasEspeciales_DIN" displayName="tblPiezasEspeciales_DIN" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tblColores_DIN" displayName="tblColores_DIN" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tblColores_DIN" displayName="tblColores_DIN" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblProveedoresExternos_DIN" displayName="tblProveedoresExternos_DIN" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblProveedoresExternos_DIN" displayName="tblProveedoresExternos_DIN" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -402,27 +402,27 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblProductos_PBK" displayName="tblProductos_PBK" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblProductos_PBK" displayName="tblProductos_PBK" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblElementosSeguridad_PBK" displayName="tblElementosSeguridad_PBK" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblElementosSeguridad_PBK" displayName="tblElementosSeguridad_PBK" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -443,34 +443,34 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tblPiezasEspeciales_PBK" displayName="tblPiezasEspeciales_PBK" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tblPiezasEspeciales_PBK" displayName="tblPiezasEspeciales_PBK" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tblColores_PBK" displayName="tblColores_PBK" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tblColores_PBK" displayName="tblColores_PBK" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tblProveedoresExternos_PBK" displayName="tblProveedoresExternos_PBK" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tblProveedoresExternos_PBK" displayName="tblProveedoresExternos_PBK" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -507,61 +507,61 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tblProductos_DRV" displayName="tblProductos_DRV" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tblProductos_DRV" displayName="tblProductos_DRV" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tblElementosSeguridad_DRV" displayName="tblElementosSeguridad_DRV" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tblElementosSeguridad_DRV" displayName="tblElementosSeguridad_DRV" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tblPiezasEspeciales_DRV" displayName="tblPiezasEspeciales_DRV" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tblPiezasEspeciales_DRV" displayName="tblPiezasEspeciales_DRV" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tblColores_DRV" displayName="tblColores_DRV" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tblColores_DRV" displayName="tblColores_DRV" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tblProveedoresExternos_DRV" displayName="tblProveedoresExternos_DRV" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tblProveedoresExternos_DRV" displayName="tblProveedoresExternos_DRV" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -614,61 +614,61 @@
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tblProductos_CAN" displayName="tblProductos_CAN" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tblProductos_CAN" displayName="tblProductos_CAN" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="tblElementosSeguridad_CAN" displayName="tblElementosSeguridad_CAN" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="tblElementosSeguridad_CAN" displayName="tblElementosSeguridad_CAN" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="tblPiezasEspeciales_CAN" displayName="tblPiezasEspeciales_CAN" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="tblPiezasEspeciales_CAN" displayName="tblPiezasEspeciales_CAN" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="tblColores_CAN" displayName="tblColores_CAN" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="tblColores_CAN" displayName="tblColores_CAN" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="tblProveedoresExternos_CAN" displayName="tblProveedoresExternos_CAN" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="tblProveedoresExternos_CAN" displayName="tblProveedoresExternos_CAN" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -705,76 +705,76 @@
 </file>
 
 <file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="tblProductos_MEZ" displayName="tblProductos_MEZ" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="tblProductos_MEZ" displayName="tblProductos_MEZ" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblProductos_SEL" displayName="tblProductos_SEL" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblProductos_SEL" displayName="tblProductos_SEL" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="tblElementosSeguridad_MEZ" displayName="tblElementosSeguridad_MEZ" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="tblElementosSeguridad_MEZ" displayName="tblElementosSeguridad_MEZ" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tblPiezasEspeciales_MEZ" displayName="tblPiezasEspeciales_MEZ" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tblPiezasEspeciales_MEZ" displayName="tblPiezasEspeciales_MEZ" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="tblColores_MEZ" displayName="tblColores_MEZ" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="tblColores_MEZ" displayName="tblColores_MEZ" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table43.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="tblProveedoresExternos_MEZ" displayName="tblProveedoresExternos_MEZ" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="tblProveedoresExternos_MEZ" displayName="tblProveedoresExternos_MEZ" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -811,73 +811,73 @@
 </file>
 
 <file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="tblProductos_CFL" displayName="tblProductos_CFL" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="tblProductos_CFL" displayName="tblProductos_CFL" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="tblElementosSeguridad_CFL" displayName="tblElementosSeguridad_CFL" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="tblElementosSeguridad_CFL" displayName="tblElementosSeguridad_CFL" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table48.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="tblPiezasEspeciales_CFL" displayName="tblPiezasEspeciales_CFL" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="tblPiezasEspeciales_CFL" displayName="tblPiezasEspeciales_CFL" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table49.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="tblColores_CFL" displayName="tblColores_CFL" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="tblColores_CFL" displayName="tblColores_CFL" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblElementosSeguridad_SEL" displayName="tblElementosSeguridad_SEL" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblElementosSeguridad_SEL" displayName="tblElementosSeguridad_SEL" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table50.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="tblProveedoresExternos_CFL" displayName="tblProveedoresExternos_CFL" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="tblProveedoresExternos_CFL" displayName="tblProveedoresExternos_CFL" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -914,95 +914,95 @@
 </file>
 
 <file path=xl/tables/table53.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="tblProductos_MZL" displayName="tblProductos_MZL" ref="I32:N57" headerRowCount="1">
-  <autoFilter ref="I32:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="tblProductos_MZL" displayName="tblProductos_MZL" ref="W4:AB29" headerRowCount="1">
+  <autoFilter ref="W4:AB29"/>
   <tableColumns count="6">
-    <tableColumn id="9" name="TipoProducto"/>
-    <tableColumn id="10" name="LargoProducto"/>
-    <tableColumn id="11" name="AnchoProducto"/>
-    <tableColumn id="12" name="AltoProducto"/>
-    <tableColumn id="13" name="PesoProducto"/>
-    <tableColumn id="14" name="CantidadPorNivel"/>
+    <tableColumn id="23" name="TipoProducto"/>
+    <tableColumn id="24" name="LargoProducto"/>
+    <tableColumn id="25" name="AnchoProducto"/>
+    <tableColumn id="26" name="AltoProducto"/>
+    <tableColumn id="27" name="PesoProducto"/>
+    <tableColumn id="28" name="CantidadPorNivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table54.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="tblElementosSeguridad_MZL" displayName="tblElementosSeguridad_MZL" ref="P32:R57" headerRowCount="1">
-  <autoFilter ref="P32:R57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="tblElementosSeguridad_MZL" displayName="tblElementosSeguridad_MZL" ref="AD4:AF29" headerRowCount="1">
+  <autoFilter ref="AD4:AF29"/>
   <tableColumns count="3">
-    <tableColumn id="16" name="Pieza"/>
-    <tableColumn id="17" name="Cantidad"/>
-    <tableColumn id="18" name="Comentario"/>
+    <tableColumn id="30" name="Pieza"/>
+    <tableColumn id="31" name="Cantidad"/>
+    <tableColumn id="32" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="tblPiezasEspeciales_MZL" displayName="tblPiezasEspeciales_MZL" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="tblPiezasEspeciales_MZL" displayName="tblPiezasEspeciales_MZL" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="tblColores_MZL" displayName="tblColores_MZL" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="tblColores_MZL" displayName="tblColores_MZL" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="tblProveedoresExternos_MZL" displayName="tblProveedoresExternos_MZL" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="tblProveedoresExternos_MZL" displayName="tblProveedoresExternos_MZL" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblPiezasEspeciales_SEL" displayName="tblPiezasEspeciales_SEL" ref="T32:V57" headerRowCount="1">
-  <autoFilter ref="T32:V57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblPiezasEspeciales_SEL" displayName="tblPiezasEspeciales_SEL" ref="AH4:AJ29" headerRowCount="1">
+  <autoFilter ref="AH4:AJ29"/>
   <tableColumns count="3">
-    <tableColumn id="20" name="Pieza"/>
-    <tableColumn id="21" name="Cantidad"/>
-    <tableColumn id="22" name="Comentario"/>
+    <tableColumn id="34" name="Pieza"/>
+    <tableColumn id="35" name="Cantidad"/>
+    <tableColumn id="36" name="Comentario"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblColores_SEL" displayName="tblColores_SEL" ref="I60:J85" headerRowCount="1">
-  <autoFilter ref="I60:J85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblColores_SEL" displayName="tblColores_SEL" ref="AL4:AM29" headerRowCount="1">
+  <autoFilter ref="AL4:AM29"/>
   <tableColumns count="2">
-    <tableColumn id="9" name="Pieza"/>
-    <tableColumn id="10" name="Color"/>
+    <tableColumn id="38" name="Pieza"/>
+    <tableColumn id="39" name="Color"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblProveedoresExternos_SEL" displayName="tblProveedoresExternos_SEL" ref="L60:M85" headerRowCount="1">
-  <autoFilter ref="L60:M85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblProveedoresExternos_SEL" displayName="tblProveedoresExternos_SEL" ref="AO4:AP29" headerRowCount="1">
+  <autoFilter ref="AO4:AP29"/>
   <tableColumns count="2">
-    <tableColumn id="12" name="Proveedor"/>
-    <tableColumn id="13" name="Alcance"/>
+    <tableColumn id="41" name="Proveedor"/>
+    <tableColumn id="42" name="Alcance"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1616,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:AP103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -1636,6 +1636,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -1716,6 +1736,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2171,6 @@
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
@@ -2377,7 +2476,6 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
@@ -2417,7 +2515,6 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
     </row>
-    <row r="74"/>
     <row r="75" ht="20.1" customHeight="1" s="8">
       <c r="A75" s="5" t="inlineStr">
         <is>
@@ -2735,7 +2832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V96"/>
+  <dimension ref="A1:AP96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -2755,6 +2852,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -2835,6 +2952,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3387,6 @@
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
@@ -3426,7 +3622,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
@@ -3466,7 +3661,6 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
     </row>
-    <row r="67"/>
     <row r="68" ht="20.1" customHeight="1" s="8">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -3566,7 +3760,6 @@
       <c r="A79" s="2" t="n"/>
       <c r="B79" s="2" t="n"/>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
@@ -3778,7 +3971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V115"/>
+  <dimension ref="A1:AP115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -3798,6 +3991,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -3878,6 +4091,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4704,6 @@
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
@@ -4519,7 +4811,6 @@
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
@@ -4668,7 +4959,6 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
@@ -5046,7 +5336,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:V"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"previewHeaders":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:U29","headers":["Peso","Alto","Frente","Fondo","Huella","ExcedenteFrente","ExcedenteFondo"],"previewHeaders":["Peso","Alto","Frente","Fondo","Huella","Exc. frente","Exc. fondo"],"aliases":[["Peso","PesoTarima","Pesotarima","Peso tarima"],["Alto","AltoTarima","Altotarima","Alto tarima"],["Frente","FrenteTarima","Frentetarima","Frente tarima"],["Fondo","FondoTarima","Fondotarima","Fondo tarima"],["Huella","HuellaTarima","Huellatarima","Huella tarima"],["ExcedenteFrente","Excedente frente","Excedentefrente"],["ExcedenteFondo","Excedente fondo","Excedentefondo"]],"previewRanges":{"SEL":"A29:G36","DIN":"A29:G36","PBK":"A29:G36","DRV":"A29:G36","MZL":"A57:G61"}},"productos":{"baseName":"tblProductos","range":"I32:N57","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"previewHeaders":["Tipo","Largo","Ancho","Alto","Peso","Cant./nivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"P32:R57","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"T32:V57","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"I60:J85","headers":["Pieza","Color"],"previewHeaders":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"L60:M85","headers":["Proveedor","Alcance"],"previewHeaders":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
+          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:AP"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"previewHeaders":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:U29","headers":["Peso","Alto","Frente","Fondo","Huella","ExcedenteFrente","ExcedenteFondo"],"previewHeaders":["Peso","Alto","Frente","Fondo","Huella","Exc. frente","Exc. fondo"],"aliases":[["Peso","PesoTarima","Pesotarima","Peso tarima"],["Alto","AltoTarima","Altotarima","Alto tarima"],["Frente","FrenteTarima","Frentetarima","Frente tarima"],["Fondo","FondoTarima","Fondotarima","Fondo tarima"],["Huella","HuellaTarima","Huellatarima","Huella tarima"],["ExcedenteFrente","Excedente frente","Excedentefrente"],["ExcedenteFondo","Excedente fondo","Excedentefondo"]],"previewRanges":{"SEL":"A29:G36","DIN":"A29:G36","PBK":"A29:G36","DRV":"A29:G36","MZL":"A57:G61"}},"productos":{"baseName":"tblProductos","range":"W4:AB29","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"previewHeaders":["Tipo","Largo","Ancho","Alto","Peso","Cant./nivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"AD4:AF29","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"AH4:AJ29","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"AL4:AM29","headers":["Pieza","Color"],"previewHeaders":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"AO4:AP29","headers":["Proveedor","Alcance"],"previewHeaders":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V92"/>
+  <dimension ref="A1:AP92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -6270,6 +6560,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -6350,6 +6660,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -6861,7 +7251,6 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
@@ -6921,7 +7310,6 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
     </row>
-    <row r="63"/>
     <row r="64" ht="20.1" customHeight="1" s="8">
       <c r="A64" s="5" t="inlineStr">
         <is>
@@ -7021,7 +7409,6 @@
       <c r="A75" s="2" t="n"/>
       <c r="B75" s="2" t="n"/>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
@@ -7227,7 +7614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:AP100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -7247,6 +7634,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -7327,6 +7734,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -7945,7 +8432,6 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="n"/>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
@@ -7985,7 +8471,6 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
     </row>
-    <row r="71"/>
     <row r="72" ht="20.1" customHeight="1" s="8">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -8085,7 +8570,6 @@
       <c r="A83" s="2" t="n"/>
       <c r="B83" s="2" t="n"/>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
@@ -8301,7 +8785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:AP100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -8321,6 +8805,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -8401,6 +8905,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9603,6 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="n"/>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
@@ -9059,7 +9642,6 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
     </row>
-    <row r="71"/>
     <row r="72" ht="20.1" customHeight="1" s="8">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -9159,7 +9741,6 @@
       <c r="A83" s="2" t="n"/>
       <c r="B83" s="2" t="n"/>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
@@ -9375,7 +9956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:AP102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -9395,6 +9976,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -9475,6 +10076,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10786,6 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
@@ -10145,7 +10825,6 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="n"/>
     </row>
-    <row r="73"/>
     <row r="74" ht="20.1" customHeight="1" s="8">
       <c r="A74" s="5" t="inlineStr">
         <is>
@@ -10461,7 +11140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:AP91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" style="8" min="1" max="1"/>
@@ -10481,6 +11160,26 @@
     <col hidden="1" width="13" customWidth="1" style="8" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" style="8" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" style="8" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="8">
@@ -10561,6 +11260,86 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TipoProducto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>LargoProducto</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>AnchoProducto</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>AltoProducto</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>PesoProducto</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CantidadPorNivel</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Pieza</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Alcance</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11853,6 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
@@ -11134,7 +11912,6 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
     </row>
-    <row r="62"/>
     <row r="63" ht="20.1" customHeight="1" s="8">
       <c r="A63" s="5" t="inlineStr">
         <is>
@@ -11234,7 +12011,6 @@
       <c r="A74" s="2" t="n"/>
       <c r="B74" s="2" t="n"/>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>

--- a/templates/FDI_Master.xlsx
+++ b/templates/FDI_Master.xlsx
@@ -295,16 +295,17 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblTarimas_DIN" displayName="tblTarimas_DIN" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblTarimas_DIN" displayName="tblTarimas_DIN" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -386,16 +387,17 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblTarimas_PBK" displayName="tblTarimas_PBK" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblTarimas_PBK" displayName="tblTarimas_PBK" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -491,16 +493,17 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tblTarimas_DRV" displayName="tblTarimas_DRV" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tblTarimas_DRV" displayName="tblTarimas_DRV" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -568,16 +571,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblTarimas_SEL" displayName="tblTarimas_SEL" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblTarimas_SEL" displayName="tblTarimas_SEL" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -598,16 +602,17 @@
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tblTarimas_CAN" displayName="tblTarimas_CAN" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tblTarimas_CAN" displayName="tblTarimas_CAN" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -689,16 +694,17 @@
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="tblTarimas_MEZ" displayName="tblTarimas_MEZ" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="tblTarimas_MEZ" displayName="tblTarimas_MEZ" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -795,16 +801,17 @@
 </file>
 
 <file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tblTarimas_CFL" displayName="tblTarimas_CFL" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tblTarimas_CFL" displayName="tblTarimas_CFL" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -898,16 +905,17 @@
 </file>
 
 <file path=xl/tables/table52.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="tblTarimas_MZL" displayName="tblTarimas_MZL" ref="O4:U29" headerRowCount="1">
-  <autoFilter ref="O4:U29"/>
-  <tableColumns count="7">
-    <tableColumn id="15" name="Peso"/>
-    <tableColumn id="16" name="Alto"/>
-    <tableColumn id="17" name="Frente"/>
-    <tableColumn id="18" name="Fondo"/>
-    <tableColumn id="19" name="Huella"/>
-    <tableColumn id="20" name="ExcedenteFrente"/>
-    <tableColumn id="21" name="ExcedenteFondo"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="tblTarimas_MZL" displayName="tblTarimas_MZL" ref="O4:V29" headerRowCount="1">
+  <autoFilter ref="O4:V29"/>
+  <tableColumns count="8">
+    <tableColumn id="15" name="Tipo"/>
+    <tableColumn id="16" name="Peso"/>
+    <tableColumn id="17" name="Alto"/>
+    <tableColumn id="18" name="Frente"/>
+    <tableColumn id="19" name="Fondo"/>
+    <tableColumn id="20" name="Excedente"/>
+    <tableColumn id="21" name="ExcedenteFrente"/>
+    <tableColumn id="22" name="ExcedenteFondo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1705,35 +1713,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -2921,35 +2934,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -4060,35 +4078,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -4721,37 +4744,42 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Exc. frente</t>
+          <t>Excedente</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Exc. fondo</t>
+          <t>Frente exced.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Fondo exced.</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:AP"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"previewHeaders":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:U29","headers":["Peso","Alto","Frente","Fondo","Huella","ExcedenteFrente","ExcedenteFondo"],"previewHeaders":["Peso","Alto","Frente","Fondo","Huella","Exc. frente","Exc. fondo"],"aliases":[["Peso","PesoTarima","Pesotarima","Peso tarima"],["Alto","AltoTarima","Altotarima","Alto tarima"],["Frente","FrenteTarima","Frentetarima","Frente tarima"],["Fondo","FondoTarima","Fondotarima","Fondo tarima"],["Huella","HuellaTarima","Huellatarima","Huella tarima"],["ExcedenteFrente","Excedente frente","Excedentefrente"],["ExcedenteFondo","Excedente fondo","Excedentefondo"]],"previewRanges":{"SEL":"A29:G36","DIN":"A29:G36","PBK":"A29:G36","DRV":"A29:G36","MZL":"A57:G61"}},"productos":{"baseName":"tblProductos","range":"W4:AB29","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"previewHeaders":["Tipo","Largo","Ancho","Alto","Peso","Cant./nivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"AD4:AF29","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"AH4:AJ29","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"AL4:AM29","headers":["Pieza","Color"],"previewHeaders":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"AO4:AP29","headers":["Proveedor","Alcance"],"previewHeaders":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
+          <t>{"version":1,"configSheet":"FDI_Table_Config","hiddenColumns":["I:AP"],"tables":{"piezas":{"baseName":"tblPiezas","range":"I4:M29","headers":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"previewHeaders":["Pieza","Comentarios","Cantidad","Unidad","Notas"],"aliases":[["Pieza","Código","Codigo"],["Comentarios","Comentario","Descripción","Descripcion"],["Cantidad"],["Unidad"],["Notas"]],"previewRanges":{"SEL":"A16:E22","DIN":"A16:E22","PBK":"A16:E22","DRV":"A16:E22","CAN":"A16:E22","MEZ":"A16:E22","CFL":"A16:E22","MZL":"A16:E22"}},"tarimas":{"baseName":"tblTarimas","range":"O4:V29","headers":["Tipo","Peso","Alto","Frente","Fondo","Excedente","ExcedenteFrente","ExcedenteFondo"],"previewHeaders":["Tipo","Peso","Alto","Frente","Fondo","Excedente","Frente exced.","Fondo exced."],"aliases":[["Tipo","TipoTarima","Tipotarima","Tipo tarima"],["Peso","PesoTarima","Pesotarima","Peso tarima"],["Alto","AltoTarima","Altotarima","Alto tarima"],["Frente","FrenteTarima","Frentetarima","Frente tarima"],["Fondo","FondoTarima","Fondotarima","Fondo tarima"],["Excedente","¿Excedente?","ExcedenteTarima","Excedente?","Excedente tarima"],["ExcedenteFrente","Excedente frente","Excedentefrente","FrenteExcedente"],["ExcedenteFondo","Excedente fondo","Excedentefondo","FondoExcedente"]],"previewRanges":{"SEL":"A29:H36","DIN":"A29:H36","PBK":"A29:H36","DRV":"A29:H36","MZL":"A57:H61"}},"productos":{"baseName":"tblProductos","range":"W4:AB29","headers":["TipoProducto","LargoProducto","AnchoProducto","AltoProducto","PesoProducto","CantidadPorNivel"],"previewHeaders":["Tipo","Largo","Ancho","Alto","Peso","Cant./nivel"],"aliases":[["TipoProducto","Tipo producto","Tipo","Producto"],["LargoProducto","Largo"],["AnchoProducto","Ancho"],["AltoProducto","Alto"],["PesoProducto","Peso","PesoPieza"],["CantidadPorNivel","Cantidad por nivel","Cantidad"]],"previewRanges":{"MEZ":"A30:F36","CFL":"A30:F36","MZL":"A49:F53"}},"elementosSeguridad":{"baseName":"tblElementosSeguridad","range":"AD4:AF29","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza","Elemento"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A52:C56","DIN":"A60:C64","PBK":"A60:C64","DRV":"A62:C66","CAN":"A51:C55","MEZ":"A63:C67","CFL":"A56:C60","MZL":"A75:C79"}},"piezasEspeciales":{"baseName":"tblPiezasEspeciales","range":"AH4:AJ29","headers":["Pieza","Cantidad","Comentario"],"previewHeaders":["Pieza","Cantidad","Comentario"],"aliases":[["Pieza"],["Cantidad"],["Comentario","Comentarios"]],"previewRanges":{"SEL":"A59:C62","DIN":"A67:C70","PBK":"A67:C70","DRV":"A69:C72","CAN":"A58:C61","MEZ":"A70:C73","CFL":"A63:C66","MZL":"A82:C85"}},"colores":{"baseName":"tblColores","range":"AL4:AM29","headers":["Pieza","Color"],"previewHeaders":["Pieza","Color"],"aliases":[["Pieza"],["Color","ColorNombre","ColorTexto"]],"previewRanges":{"SEL":"A71:B75","DIN":"A79:B83","PBK":"A79:B83","DRV":"A81:B85","CAN":"A70:B74","MEZ":"A82:B86","CFL":"A75:B79","MZL":"A94:B98"}},"proveedoresExternos":{"baseName":"tblProveedoresExternos","range":"AO4:AP29","headers":["Proveedor","Alcance"],"previewHeaders":["Proveedor","Alcance"],"aliases":[["Proveedor"],["Alcance","Comentarios"]],"previewRanges":{"SEL":"A87:B90","DIN":"A95:B98","PBK":"A95:B98","DRV":"A97:B100","CAN":"A86:B89","MEZ":"A98:B101","CFL":"A91:B94","MZL":"A110:B113"}}}}</t>
         </is>
       </c>
     </row>
@@ -6629,35 +6657,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -6951,37 +6984,42 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Exc. frente</t>
+          <t>Excedente</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Exc. fondo</t>
+          <t>Frente exced.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fondo exced.</t>
         </is>
       </c>
     </row>
@@ -7703,35 +7741,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -8025,37 +8068,42 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Exc. frente</t>
+          <t>Excedente</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Exc. fondo</t>
+          <t>Frente exced.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fondo exced.</t>
         </is>
       </c>
     </row>
@@ -8874,35 +8922,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -9196,37 +9249,42 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Exc. frente</t>
+          <t>Excedente</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Exc. fondo</t>
+          <t>Frente exced.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fondo exced.</t>
         </is>
       </c>
     </row>
@@ -10045,35 +10103,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
@@ -10367,37 +10430,42 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Exc. frente</t>
+          <t>Excedente</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Exc. fondo</t>
+          <t>Frente exced.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fondo exced.</t>
         </is>
       </c>
     </row>
@@ -11229,35 +11297,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Frente</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Fondo</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Huella</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>Excedente</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>ExcedenteFrente</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>ExcedenteFondo</t>
         </is>
